--- a/public/exports-with-coowners/11715311.xlsx
+++ b/public/exports-with-coowners/11715311.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311017829</t>
+          <t xml:space="preserve">311017836</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123153</t>
+          <t xml:space="preserve">311123156</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">

--- a/public/exports-with-coowners/11715311.xlsx
+++ b/public/exports-with-coowners/11715311.xlsx
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 30</t>
+          <t xml:space="preserve">Nymøllevej 38</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060987</t>
+          <t xml:space="preserve">2060298</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5010,11 +5010,11 @@
         </is>
       </c>
       <c r="J67">
-        <v>360</v>
+        <v>807</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311090351</t>
+          <t xml:space="preserve">311092119</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-09</t>
+          <t xml:space="preserve">2025-01-22</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nymøllevej 38</t>
+          <t xml:space="preserve">Rustenborgvej 19A</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060298</t>
+          <t xml:space="preserve">8864451</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,11 +5085,11 @@
         </is>
       </c>
       <c r="J68">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092119</t>
+          <t xml:space="preserve">311092129</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 19A</t>
+          <t xml:space="preserve">Toftebæksvej 38</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864451</t>
+          <t xml:space="preserve">9166452</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5160,11 +5160,11 @@
         </is>
       </c>
       <c r="J69">
-        <v>819</v>
+        <v>377</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092129</t>
+          <t xml:space="preserve">311092130</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 38</t>
+          <t xml:space="preserve">Trongårdsvej 58</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,20 +5226,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">9166452</t>
+          <t xml:space="preserve">8864449</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J70">
-        <v>377</v>
+        <v>527</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092130</t>
+          <t xml:space="preserve">311092132</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 58</t>
+          <t xml:space="preserve">Hjortholmsvej 6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864449</t>
+          <t xml:space="preserve">2028340</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>527</v>
+        <v>339</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311092132</t>
+          <t xml:space="preserve">311095074</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-22</t>
+          <t xml:space="preserve">2025-02-11</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmsvej 6</t>
+          <t xml:space="preserve">Virumgårdsvej 22A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028340</t>
+          <t xml:space="preserve">2103443</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,11 +5385,11 @@
         </is>
       </c>
       <c r="J72">
-        <v>339</v>
+        <v>690</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311095074</t>
+          <t xml:space="preserve">311096443</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-11</t>
+          <t xml:space="preserve">2025-02-19</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 22A</t>
+          <t xml:space="preserve">Virumgårdsvej 22B</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,20 +5451,20 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103443</t>
+          <t xml:space="preserve">8864754</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J73">
-        <v>690</v>
+        <v>712</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096443</t>
+          <t xml:space="preserve">311096444</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 22B</t>
+          <t xml:space="preserve">Virumgårdsvej 22C</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5531,15 +5531,15 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J74">
-        <v>712</v>
+        <v>824</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096444</t>
+          <t xml:space="preserve">311096445</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 22C</t>
+          <t xml:space="preserve">Virumgårdsvej 2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864754</t>
+          <t xml:space="preserve">2103482</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>824</v>
+        <v>374</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311096445</t>
+          <t xml:space="preserve">311098179</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-02-19</t>
+          <t xml:space="preserve">2025-03-02</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumgårdsvej 2</t>
+          <t xml:space="preserve">Virumvej 35</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103482</t>
+          <t xml:space="preserve">8864754</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5685,11 +5685,11 @@
         </is>
       </c>
       <c r="J76">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098179</t>
+          <t xml:space="preserve">311098180</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5741,17 +5741,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumvej 35</t>
+          <t xml:space="preserve">Jernbanepladsen 22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864754</t>
+          <t xml:space="preserve">2030553</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5760,11 +5760,11 @@
         </is>
       </c>
       <c r="J77">
-        <v>350</v>
+        <v>904</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311098180</t>
+          <t xml:space="preserve">311104767</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-03-02</t>
+          <t xml:space="preserve">2025-04-01</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanepladsen 22</t>
+          <t xml:space="preserve">Jernbanevej 16</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030553</t>
+          <t xml:space="preserve">2030573</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5835,11 +5835,11 @@
         </is>
       </c>
       <c r="J78">
-        <v>904</v>
+        <v>436</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104767</t>
+          <t xml:space="preserve">311104762</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanevej 16</t>
+          <t xml:space="preserve">Rustenborgvej 1C</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030573</t>
+          <t xml:space="preserve">2030225</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5910,11 +5910,11 @@
         </is>
       </c>
       <c r="J79">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104762</t>
+          <t xml:space="preserve">311104760</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 1C</t>
+          <t xml:space="preserve">Rustenborgvej 2A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030225</t>
+          <t xml:space="preserve">2030254</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5985,11 +5985,11 @@
         </is>
       </c>
       <c r="J80">
-        <v>442</v>
+        <v>296</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104760</t>
+          <t xml:space="preserve">311104759</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 2A</t>
+          <t xml:space="preserve">Rustenborgvej 3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030254</t>
+          <t xml:space="preserve">2030252</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="J81">
-        <v>296</v>
+        <v>444</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104759</t>
+          <t xml:space="preserve">311104755</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rustenborgvej 3</t>
+          <t xml:space="preserve">Nørregade 9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030252</t>
+          <t xml:space="preserve">8864425</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6135,11 +6135,11 @@
         </is>
       </c>
       <c r="J82">
-        <v>444</v>
+        <v>265</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311104755</t>
+          <t xml:space="preserve">311107735</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-01</t>
+          <t xml:space="preserve">2025-04-20</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 9</t>
+          <t xml:space="preserve">Sorgenfrivej 13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864425</t>
+          <t xml:space="preserve">2029916</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6210,11 +6210,11 @@
         </is>
       </c>
       <c r="J83">
-        <v>265</v>
+        <v>502</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311107735</t>
+          <t xml:space="preserve">311107784</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6266,40 +6266,40 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorgenfrivej 13</t>
+          <t xml:space="preserve">Taarbæk Strandvej 84</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029916</t>
+          <t xml:space="preserve">2047087</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J84">
-        <v>502</v>
+        <v>545</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311107784</t>
+          <t xml:space="preserve">311123153</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning Aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-20</t>
+          <t xml:space="preserve">2025-07-03</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,40 +6341,40 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taarbæk Strandvej 84</t>
+          <t xml:space="preserve">Hasselvej 74B</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047087</t>
+          <t xml:space="preserve">1301698</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J85">
-        <v>545</v>
+        <v>298</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311123156</t>
+          <t xml:space="preserve">311136466</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning Aps</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-03</t>
+          <t xml:space="preserve">2025-09-24</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6431,15 +6431,15 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J86">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311136466</t>
+          <t xml:space="preserve">311136474</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6491,40 +6491,40 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hasselvej 74B</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301698</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J87">
-        <v>355</v>
+        <v>846</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311136474</t>
+          <t xml:space="preserve">311139246</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning Aps</t>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-24</t>
+          <t xml:space="preserve">2025-10-09</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Buddingevej 39</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,30 +6576,30 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">2064573</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J88">
-        <v>846</v>
+        <v>334</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311139246</t>
+          <t xml:space="preserve">311145808</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
+          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK aps</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-09</t>
+          <t xml:space="preserve">2025-11-17</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,40 +6641,40 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buddingevej 39</t>
+          <t xml:space="preserve">Askevænget 10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064573</t>
+          <t xml:space="preserve">1301698</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J89">
-        <v>334</v>
+        <v>1060</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311145808</t>
+          <t xml:space="preserve">311150499</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRANEKAER-ARKITEKTKONTOR.DK aps</t>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-17</t>
+          <t xml:space="preserve">2025-12-16</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,30 +6716,30 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askevænget 10</t>
+          <t xml:space="preserve">Nøjsomhedsvej 11</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301698</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J90">
-        <v>1060</v>
+        <v>634</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311150499</t>
+          <t xml:space="preserve">311176540</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-16</t>
+          <t xml:space="preserve">2026-05-13</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 11</t>
+          <t xml:space="preserve">Lyngby Torv 16</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,20 +6801,20 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2030182</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J91">
-        <v>634</v>
+        <v>266</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311176540</t>
+          <t xml:space="preserve">311179524</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-13</t>
+          <t xml:space="preserve">2026-05-30</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Torv 16</t>
+          <t xml:space="preserve">Hjortholmsvej 3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030182</t>
+          <t xml:space="preserve">2028337</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="J92">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311179524</t>
+          <t xml:space="preserve">311195275</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-30</t>
+          <t xml:space="preserve">2026-08-18</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,30 +6941,30 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmsvej 3</t>
+          <t xml:space="preserve">Kongsvænget 10C</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028337</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J93">
-        <v>356</v>
+        <v>853</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311195275</t>
+          <t xml:space="preserve">311196141</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-18</t>
+          <t xml:space="preserve">2026-08-23</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10C</t>
+          <t xml:space="preserve">Grønnevej 218</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">2103430</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J94">
-        <v>853</v>
+        <v>813</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311196141</t>
+          <t xml:space="preserve">311198636</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-23</t>
+          <t xml:space="preserve">2026-09-05</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7086,55 +7086,55 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">173</t>
+          <t xml:space="preserve">190</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 218</t>
+          <t xml:space="preserve">Lejrvej 47</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103430</t>
+          <t xml:space="preserve">2134936</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J95">
-        <v>813</v>
+        <v>636</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311198636</t>
+          <t xml:space="preserve">311231307</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">Energitjenesten Øst</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-05</t>
+          <t xml:space="preserve">2027-02-08</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -7161,45 +7161,45 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">190</t>
+          <t xml:space="preserve">173</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvej 47</t>
+          <t xml:space="preserve">Christian X's Alle 95C</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134936</t>
+          <t xml:space="preserve">206570</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
-        <v>636</v>
+        <v>300</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231307</t>
+          <t xml:space="preserve">311230119</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energitjenesten Øst</t>
+          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-08</t>
+          <t xml:space="preserve">2027-02-23</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95C</t>
+          <t xml:space="preserve">Christian X's Alle 95D</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J97">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230119</t>
+          <t xml:space="preserve">311230118</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95D</t>
+          <t xml:space="preserve">Christian X's Alle 95E</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7331,15 +7331,15 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J98">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230118</t>
+          <t xml:space="preserve">311230107</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95E</t>
+          <t xml:space="preserve">Engelsborgvej 66</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,30 +7401,30 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">206570</t>
+          <t xml:space="preserve">1301455</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J99">
-        <v>450</v>
+        <v>1774</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230107</t>
+          <t xml:space="preserve">311245601</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arkitektfirmaet Byg &amp; Bo ApS</t>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-23</t>
+          <t xml:space="preserve">2027-05-05</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7476,20 +7476,20 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301455</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>1774</v>
+        <v>680</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245601</t>
+          <t xml:space="preserve">311245596</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7556,15 +7556,15 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J101">
-        <v>680</v>
+        <v>1946</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245596</t>
+          <t xml:space="preserve">311245602</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelsborgvej 66</t>
+          <t xml:space="preserve">Toftebæksvej 8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,20 +7626,20 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">8864411</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J102">
-        <v>1946</v>
+        <v>942</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311245602</t>
+          <t xml:space="preserve">311251199</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-05</t>
+          <t xml:space="preserve">2027-06-01</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 8</t>
+          <t xml:space="preserve">Ravnholmvej 7</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864411</t>
+          <t xml:space="preserve">2062047</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J103">
-        <v>942</v>
+        <v>266</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251199</t>
+          <t xml:space="preserve">311290836</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-01</t>
+          <t xml:space="preserve">2028-01-02</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,17 +7766,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnholmvej 7</t>
+          <t xml:space="preserve">Taarbæk Strandvej 90</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2062047</t>
+          <t xml:space="preserve">2047232</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290836</t>
+          <t xml:space="preserve">311290924</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-02</t>
+          <t xml:space="preserve">2028-01-03</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taarbæk Strandvej 90</t>
+          <t xml:space="preserve">Caroline Amalie Vej 118</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047232</t>
+          <t xml:space="preserve">8864558</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>295</v>
+        <v>864</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290924</t>
+          <t xml:space="preserve">311295408</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-03</t>
+          <t xml:space="preserve">2028-01-31</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 118</t>
+          <t xml:space="preserve">Caroline Amalie Vej 120</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J106">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295408</t>
+          <t xml:space="preserve">311295440</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 120</t>
+          <t xml:space="preserve">Caroline Amalie Vej 122</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8006,15 +8006,15 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J107">
-        <v>864</v>
+        <v>969</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295440</t>
+          <t xml:space="preserve">311295444</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 122</t>
+          <t xml:space="preserve">Caroline Amalie Vej 124</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8081,15 +8081,15 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J108">
-        <v>969</v>
+        <v>658</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295444</t>
+          <t xml:space="preserve">311295460</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 124</t>
+          <t xml:space="preserve">Caroline Amalie Vej 126</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8156,15 +8156,15 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J109">
-        <v>658</v>
+        <v>3833</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295460</t>
+          <t xml:space="preserve">311295495</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Caroline Amalie Vej 126</t>
+          <t xml:space="preserve">Lyngby Hovedgade 102A</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,20 +8226,20 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864558</t>
+          <t xml:space="preserve">2065603</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J110">
-        <v>3833</v>
+        <v>2277</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295495</t>
+          <t xml:space="preserve">311298110</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-31</t>
+          <t xml:space="preserve">2028-02-16</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 102A</t>
+          <t xml:space="preserve">Christian X's Alle 97A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065603</t>
+          <t xml:space="preserve">100497999</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J111">
-        <v>2277</v>
+        <v>280</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298110</t>
+          <t xml:space="preserve">311306901</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-16</t>
+          <t xml:space="preserve">2028-04-06</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 97A</t>
+          <t xml:space="preserve">Sorgenfrigårdsvej 37</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,20 +8376,20 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">100497999</t>
+          <t xml:space="preserve">2029392</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J112">
-        <v>280</v>
+        <v>317</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306901</t>
+          <t xml:space="preserve">311313170</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-06</t>
+          <t xml:space="preserve">2028-05-09</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorgenfrigårdsvej 37</t>
+          <t xml:space="preserve">Fuglevadsvej 49</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029392</t>
+          <t xml:space="preserve">1300682</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -8460,11 +8460,11 @@
         </is>
       </c>
       <c r="J113">
-        <v>317</v>
+        <v>1035</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311313170</t>
+          <t xml:space="preserve">311315069</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-09</t>
+          <t xml:space="preserve">2028-05-18</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevadsvej 49</t>
+          <t xml:space="preserve">Ravnholmvej 11</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300682</t>
+          <t xml:space="preserve">2060774</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -8535,11 +8535,11 @@
         </is>
       </c>
       <c r="J114">
-        <v>1035</v>
+        <v>2508</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311315069</t>
+          <t xml:space="preserve">311317367</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-18</t>
+          <t xml:space="preserve">2028-05-30</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnholmvej 11</t>
+          <t xml:space="preserve">Kulsviervej 5</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,30 +8601,30 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060774</t>
+          <t xml:space="preserve">2062257</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J115">
-        <v>2508</v>
+        <v>264</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311317367</t>
+          <t xml:space="preserve">311319303</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-05-30</t>
+          <t xml:space="preserve">2028-06-08</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulsviervej 5</t>
+          <t xml:space="preserve">Toftebæksvej 17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,25 +8676,25 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2062257</t>
+          <t xml:space="preserve">8864437</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J116">
-        <v>264</v>
+        <v>850</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319303</t>
+          <t xml:space="preserve">311319296</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -8741,17 +8741,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 17</t>
+          <t xml:space="preserve">Grønnevej 218</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864437</t>
+          <t xml:space="preserve">2103430</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>850</v>
+        <v>3585</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319296</t>
+          <t xml:space="preserve">311324386</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-06-08</t>
+          <t xml:space="preserve">2028-07-03</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8831,15 +8831,15 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J118">
-        <v>3585</v>
+        <v>640</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324386</t>
+          <t xml:space="preserve">311324387</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8906,15 +8906,15 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J119">
-        <v>640</v>
+        <v>1326</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324387</t>
+          <t xml:space="preserve">311324386</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 218</t>
+          <t xml:space="preserve">Geels Plads 40</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,20 +8976,20 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103430</t>
+          <t xml:space="preserve">2074600</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>1326</v>
+        <v>3579</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311324386</t>
+          <t xml:space="preserve">311330677</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-07-03</t>
+          <t xml:space="preserve">2028-08-15</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,30 +9041,30 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geels Plads 40</t>
+          <t xml:space="preserve">Trongårdsvej 50</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2074600</t>
+          <t xml:space="preserve">8864449</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J121">
-        <v>3579</v>
+        <v>986</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330677</t>
+          <t xml:space="preserve">311330689</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9131,15 +9131,15 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>986</v>
+        <v>6598</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330689</t>
+          <t xml:space="preserve">311331058</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-15</t>
+          <t xml:space="preserve">2028-08-17</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trongårdsvej 50</t>
+          <t xml:space="preserve">Kongevejen 55</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,20 +9201,20 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864449</t>
+          <t xml:space="preserve">2028010</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J123">
-        <v>6598</v>
+        <v>1575</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311331058</t>
+          <t xml:space="preserve">311333738</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-17</t>
+          <t xml:space="preserve">2028-08-31</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9281,11 +9281,11 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J124">
-        <v>1575</v>
+        <v>370</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 55</t>
+          <t xml:space="preserve">Kongevejen 57</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9356,11 +9356,11 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>370</v>
+        <v>535</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 57</t>
+          <t xml:space="preserve">Lyngbygårdsvej 37</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028010</t>
+          <t xml:space="preserve">2029334</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -9435,21 +9435,21 @@
         </is>
       </c>
       <c r="J126">
-        <v>535</v>
+        <v>6394</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311333738</t>
+          <t xml:space="preserve">311336039</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-31</t>
+          <t xml:space="preserve">2028-09-13</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9506,11 +9506,11 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J127">
-        <v>6394</v>
+        <v>503</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -9566,40 +9566,40 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngbygårdsvej 37</t>
+          <t xml:space="preserve">Kongsvænget 10B</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029334</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J128">
-        <v>503</v>
+        <v>2552</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336039</t>
+          <t xml:space="preserve">311336294</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-13</t>
+          <t xml:space="preserve">2028-09-14</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,17 +9641,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Lyngby Hovedgade 28</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">2030466</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>3540</v>
+        <v>4499</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311337951</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-09-25</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Nybrovej 401B</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">8864737</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,21 +9735,21 @@
         </is>
       </c>
       <c r="J130">
-        <v>428</v>
+        <v>497</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311339703</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-10-04</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10</t>
+          <t xml:space="preserve">Becksvej 3</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">2047221</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,21 +9810,21 @@
         </is>
       </c>
       <c r="J131">
-        <v>431</v>
+        <v>327</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311345047</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,40 +9866,40 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongsvænget 10B</t>
+          <t xml:space="preserve">Lyngby Hovedgade 1A</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030815</t>
+          <t xml:space="preserve">203119</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J132">
-        <v>2552</v>
+        <v>3922</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336294</t>
+          <t xml:space="preserve">311345064</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-14</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 28</t>
+          <t xml:space="preserve">Taarbæk Strandvej 96A</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030466</t>
+          <t xml:space="preserve">2047221</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,21 +9960,21 @@
         </is>
       </c>
       <c r="J133">
-        <v>4499</v>
+        <v>2624</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337951</t>
+          <t xml:space="preserve">311345057</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi og Rådgivning ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-09-25</t>
+          <t xml:space="preserve">2028-11-05</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nybrovej 401B</t>
+          <t xml:space="preserve">Bauneporten 20</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,20 +10026,20 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864737</t>
+          <t xml:space="preserve">2029353</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J134">
-        <v>497</v>
+        <v>3101</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339703</t>
+          <t xml:space="preserve">311346074</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-04</t>
+          <t xml:space="preserve">2028-11-09</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,40 +10091,40 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Becksvej 3</t>
+          <t xml:space="preserve">Skolebakken 9</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047221</t>
+          <t xml:space="preserve">8139785</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J135">
-        <v>327</v>
+        <v>16483</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345047</t>
+          <t xml:space="preserve">311353958</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2029-01-09</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 1A</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">203119</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10185,11 +10185,11 @@
         </is>
       </c>
       <c r="J136">
-        <v>3922</v>
+        <v>4637</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345064</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,30 +10241,30 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Taarbæk Strandvej 96A</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2047221</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J137">
-        <v>2624</v>
+        <v>3693</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311345057</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-05</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bauneporten 20</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10326,20 +10326,20 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029353</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J138">
-        <v>3101</v>
+        <v>1405</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311346074</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,40 +10391,40 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 9</t>
+          <t xml:space="preserve">Lundtoftevej 53A</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8139785</t>
+          <t xml:space="preserve">8864426</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J139">
-        <v>16483</v>
+        <v>3674</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311353958</t>
+          <t xml:space="preserve">311361942</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-09</t>
+          <t xml:space="preserve">2029-02-28</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Gyrithe Lemches Vej 14</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10481,15 +10481,15 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J140">
-        <v>4637</v>
+        <v>908</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311362217</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2029-03-01</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Christian X's Alle 95A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,20 +10551,20 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">206570</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J141">
-        <v>3693</v>
+        <v>1790</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311367421</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2029-03-27</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Christian X's Alle 95B</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,20 +10626,20 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">206568, 206569</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J142">
-        <v>1405</v>
+        <v>782</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311367239</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2029-03-27</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 53A</t>
+          <t xml:space="preserve">Christian X's Alle 113</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,30 +10701,30 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">1301456</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>3674</v>
+        <v>266</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311361942</t>
+          <t xml:space="preserve">311481297</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-28</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyrithe Lemches Vej 14</t>
+          <t xml:space="preserve">Kulsviervej 115</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,20 +10776,20 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864426</t>
+          <t xml:space="preserve">2060251</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J144">
-        <v>908</v>
+        <v>470</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311362217</t>
+          <t xml:space="preserve">311481296</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-01</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95A</t>
+          <t xml:space="preserve">Lundtoftevej 212</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">206570</t>
+          <t xml:space="preserve">2061449</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>1790</v>
+        <v>263</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367421</t>
+          <t xml:space="preserve">311481407</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-27</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 95B</t>
+          <t xml:space="preserve">Lyngby Hovedgade 70C</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">206568, 206569</t>
+          <t xml:space="preserve">100052, 100053, 100054, 100055</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J146">
-        <v>782</v>
+        <v>432</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367239</t>
+          <t xml:space="preserve">311481300</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-27</t>
+          <t xml:space="preserve">2030-12-08</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 113</t>
+          <t xml:space="preserve">Lyngby Hovedgade 1C</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301456</t>
+          <t xml:space="preserve">100052706</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,21 +11010,21 @@
         </is>
       </c>
       <c r="J147">
-        <v>266</v>
+        <v>591</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481297</t>
+          <t xml:space="preserve">311520638</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulsviervej 115</t>
+          <t xml:space="preserve">Åstræde 1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2060251</t>
+          <t xml:space="preserve">8864464</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>470</v>
+        <v>913</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481296</t>
+          <t xml:space="preserve">311520617</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2031-05-17</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundtoftevej 212</t>
+          <t xml:space="preserve">Rævehøjparken 1</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061449</t>
+          <t xml:space="preserve">212522, 100645398, 100645399, 100645400, 100645401, 100645402, 100645403, 100645404, 100645405, 100645406, 100645407, 100645408, 100645409, 100645410, 100645411, 100645412, 100645413, 100645414, 100645415, 100645416, 100645417, 100645418, 100645419, 100645420, 100645421, 100645422, 100645423, 100645424, 100645425, 100645426, 100645427</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,21 +11160,21 @@
         </is>
       </c>
       <c r="J149">
-        <v>263</v>
+        <v>1848</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481407</t>
+          <t xml:space="preserve">311534879</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2031-07-09</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 70C</t>
+          <t xml:space="preserve">Rævehøjparken 11</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,30 +11226,30 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052, 100053, 100054, 100055</t>
+          <t xml:space="preserve">100645428, 100645429, 100645430, 100645431, 100645432, 100645433, 100645434, 100645435, 100645436, 100645437, 100645438, 100645439, 100645440, 100645441, 100645442, 100645443, 100645444, 100645445, 100645446, 100645447, 100645448, 100645449, 100645450, 100645451, 100645452, 100645453, 100645454, 100645455, 100645456, 100645457</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J150">
-        <v>432</v>
+        <v>1848</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481300</t>
+          <t xml:space="preserve">311534879</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-08</t>
+          <t xml:space="preserve">2031-07-09</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Hovedgade 1C</t>
+          <t xml:space="preserve">Rævehøjparken 2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,30 +11301,30 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052706</t>
+          <t xml:space="preserve">100645397, 100645461, 100645462, 100645464, 100645465, 100645466, 100645469, 100645471, 100645473, 100645474, 100645475, 100645476, 100645477, 100645479, 100645481, 100645482, 100645483, 100645484, 100645485, 100645487, 100645458, 100645459, 100645460, 100645463, 100645467, 100645468, 100645470, 100645472, 100645478, 100645480, 100645486</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J151">
-        <v>591</v>
+        <v>1850</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520638</t>
+          <t xml:space="preserve">311534879</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-07-09</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åstræde 1</t>
+          <t xml:space="preserve">Høstvej 12</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864464</t>
+          <t xml:space="preserve">2029365</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,21 +11385,21 @@
         </is>
       </c>
       <c r="J152">
-        <v>913</v>
+        <v>386</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311520617</t>
+          <t xml:space="preserve">311569627</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-17</t>
+          <t xml:space="preserve">2031-12-22</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævehøjparken 1</t>
+          <t xml:space="preserve">Høstvej 14</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,30 +11451,30 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">212522, 100645398, 100645399, 100645400, 100645401, 100645402, 100645403, 100645404, 100645405, 100645406, 100645407, 100645408, 100645409, 100645410, 100645411, 100645412, 100645413, 100645414, 100645415, 100645416, 100645417, 100645418, 100645419, 100645420, 100645421, 100645422, 100645423, 100645424, 100645425, 100645426, 100645427</t>
+          <t xml:space="preserve">2029365</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J153">
-        <v>1848</v>
+        <v>566</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534879</t>
+          <t xml:space="preserve">311569627</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-09</t>
+          <t xml:space="preserve">2031-12-22</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11501,12 +11501,12 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -11516,40 +11516,40 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævehøjparken 11</t>
+          <t xml:space="preserve">Virumvej 127</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">100645428, 100645429, 100645430, 100645431, 100645432, 100645433, 100645434, 100645435, 100645436, 100645437, 100645438, 100645439, 100645440, 100645441, 100645442, 100645443, 100645444, 100645445, 100645446, 100645447, 100645448, 100645449, 100645450, 100645451, 100645452, 100645453, 100645454, 100645455, 100645456, 100645457</t>
+          <t xml:space="preserve">212323, 212324</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>1848</v>
+        <v>2065</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534879</t>
+          <t xml:space="preserve">311571303</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-09</t>
+          <t xml:space="preserve">2032-01-07</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11576,12 +11576,12 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -11591,40 +11591,40 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rævehøjparken 2</t>
+          <t xml:space="preserve">Virumvej 123</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">100645397, 100645461, 100645462, 100645464, 100645465, 100645466, 100645469, 100645471, 100645473, 100645474, 100645475, 100645476, 100645477, 100645479, 100645481, 100645482, 100645483, 100645484, 100645485, 100645487, 100645458, 100645459, 100645460, 100645463, 100645467, 100645468, 100645470, 100645472, 100645478, 100645480, 100645486</t>
+          <t xml:space="preserve">414123, 414124</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>1850</v>
+        <v>2349</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311534879</t>
+          <t xml:space="preserve">311571532</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-09</t>
+          <t xml:space="preserve">2032-01-10</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11651,12 +11651,12 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -11666,17 +11666,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høstvej 12</t>
+          <t xml:space="preserve">Sennepsmarken 1</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029365</t>
+          <t xml:space="preserve">214823, 214825, 214824, 214826</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,21 +11685,21 @@
         </is>
       </c>
       <c r="J156">
-        <v>386</v>
+        <v>5774</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569627</t>
+          <t xml:space="preserve">311576205</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-22</t>
+          <t xml:space="preserve">2032-02-02</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">LYNGBY BOLIGSELSKAB</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Høstvej 14</t>
+          <t xml:space="preserve">Bauneporten 22</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,30 +11751,30 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029365</t>
+          <t xml:space="preserve">205789, 205790</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>566</v>
+        <v>2207</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569627</t>
+          <t xml:space="preserve">311605065</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-22</t>
+          <t xml:space="preserve">2032-06-02</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumvej 127</t>
+          <t xml:space="preserve">Asylgade 9A</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">212323, 212324</t>
+          <t xml:space="preserve">1300767</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,21 +11835,21 @@
         </is>
       </c>
       <c r="J158">
-        <v>2065</v>
+        <v>940</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571303</t>
+          <t xml:space="preserve">311609045</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-07</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -11891,17 +11891,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Virumvej 123</t>
+          <t xml:space="preserve">Emil Pipers Vej 5</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">414123, 414124</t>
+          <t xml:space="preserve">2064737</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,21 +11910,21 @@
         </is>
       </c>
       <c r="J159">
-        <v>2349</v>
+        <v>1173</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571532</t>
+          <t xml:space="preserve">311609052</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-10</t>
+          <t xml:space="preserve">2032-06-20</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11951,12 +11951,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -11966,17 +11966,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sennepsmarken 1</t>
+          <t xml:space="preserve">Baunehøjvej 6</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">214823, 214825, 214824, 214826</t>
+          <t xml:space="preserve">2029257</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,21 +11985,21 @@
         </is>
       </c>
       <c r="J160">
-        <v>5774</v>
+        <v>1110</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576205</t>
+          <t xml:space="preserve">311614560</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-02</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">LYNGBY BOLIGSELSKAB</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bauneporten 22</t>
+          <t xml:space="preserve">Carlshøjvej 7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">205789, 205790</t>
+          <t xml:space="preserve">2029261</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -12060,21 +12060,21 @@
         </is>
       </c>
       <c r="J161">
-        <v>2207</v>
+        <v>1908</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605065</t>
+          <t xml:space="preserve">311614576</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-02</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 9A</t>
+          <t xml:space="preserve">Kastanievej 4A</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300767</t>
+          <t xml:space="preserve">2030205</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,11 +12135,11 @@
         </is>
       </c>
       <c r="J162">
-        <v>940</v>
+        <v>1512</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609045</t>
+          <t xml:space="preserve">311614565</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emil Pipers Vej 5</t>
+          <t xml:space="preserve">Melagervej 1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064737</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>1173</v>
+        <v>328</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311609052</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-20</t>
+          <t xml:space="preserve">2032-07-11</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunehøjvej 6</t>
+          <t xml:space="preserve">Melagervej 13</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029257</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J164">
-        <v>1110</v>
+        <v>656</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614560</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carlshøjvej 7</t>
+          <t xml:space="preserve">Melagervej 21</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029261</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J165">
-        <v>1908</v>
+        <v>656</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614576</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanievej 4A</t>
+          <t xml:space="preserve">Melagervej 5</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030205</t>
+          <t xml:space="preserve">2029397</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J166">
-        <v>1512</v>
+        <v>656</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614565</t>
+          <t xml:space="preserve">311614555</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 1</t>
+          <t xml:space="preserve">Rønne Alle 2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">2063646</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>328</v>
+        <v>1968</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311614558</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,30 +12566,30 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 13</t>
+          <t xml:space="preserve">Furesøvej 161</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">1301632</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J168">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311618189</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-08-02</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,30 +12641,30 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 21</t>
+          <t xml:space="preserve">Furesøvej 163</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">1301632</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J169">
-        <v>656</v>
+        <v>291</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311618186</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-08-02</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12701,12 +12701,12 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melagervej 5</t>
+          <t xml:space="preserve">Bredebovej 5</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,30 +12726,30 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029397</t>
+          <t xml:space="preserve">203683, 203684</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>656</v>
+        <v>14925</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614555</t>
+          <t xml:space="preserve">311626375</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-09-08</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rønne Alle 2</t>
+          <t xml:space="preserve">Lyngby Kirkestræde 8B</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2063646</t>
+          <t xml:space="preserve">2030014</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -12810,11 +12810,11 @@
         </is>
       </c>
       <c r="J171">
-        <v>1968</v>
+        <v>448</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614558</t>
+          <t xml:space="preserve">311628911</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-11</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,17 +12866,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furesøvej 161</t>
+          <t xml:space="preserve">Hjortholmsvej 7</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301632</t>
+          <t xml:space="preserve">2028658</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -12885,21 +12885,21 @@
         </is>
       </c>
       <c r="J172">
-        <v>552</v>
+        <v>306</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311618189</t>
+          <t xml:space="preserve">311646859</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">TT-Energioptimering</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-02</t>
+          <t xml:space="preserve">2032-12-02</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,40 +12941,40 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Furesøvej 163</t>
+          <t xml:space="preserve">Firskovvej 41</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2830</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301632</t>
+          <t xml:space="preserve">10180201</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J173">
-        <v>291</v>
+        <v>1556</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311618186</t>
+          <t xml:space="preserve">311665365</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-02</t>
+          <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13001,12 +13001,12 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby almennyttige Boligselskab</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredebovej 5</t>
+          <t xml:space="preserve">Slotsvænget 23A</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,7 +13026,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">203683, 203684</t>
+          <t xml:space="preserve">8864457</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -13035,21 +13035,21 @@
         </is>
       </c>
       <c r="J174">
-        <v>14925</v>
+        <v>1832</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626375</t>
+          <t xml:space="preserve">311665366</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-08</t>
+          <t xml:space="preserve">2033-03-09</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby Kirkestræde 8B</t>
+          <t xml:space="preserve">Sorgenfrivej 21</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030014</t>
+          <t xml:space="preserve">2029965</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -13110,21 +13110,21 @@
         </is>
       </c>
       <c r="J175">
-        <v>448</v>
+        <v>260</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311628911</t>
+          <t xml:space="preserve">311665962</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjortholmsvej 7</t>
+          <t xml:space="preserve">Eremitageparken 103</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,30 +13176,30 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028658</t>
+          <t xml:space="preserve">204081, 204082, 204083, 204084, 204085, 204086, 204087, 204088, 204090, 204091, 204092, 204093, 204094, 204095, 204106, 204096, 204097, 204102, 204105, 204109, 204114, 204098, 204101, 204103, 204104, 204107, 204108, 204110, 204112, 204113, 204115, 204116, 204118, 204119, 204117, 204120, 204121, 204123, 204124, 204125, 204126, 204127, 204128</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J176">
-        <v>306</v>
+        <v>3112</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646859</t>
+          <t xml:space="preserve">311721371</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t xml:space="preserve">TT-Energioptimering</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-02</t>
+          <t xml:space="preserve">2033-11-10</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13226,12 +13226,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Firskovvej 41</t>
+          <t xml:space="preserve">Eremitageparken 11</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180201</t>
+          <t xml:space="preserve">204044, 211172, 211184, 211206, 204045, 204056, 210751, 211217, 211617, 211627, 211661, 212015, 212026, 212063, 204067, 204078, 204089, 204100, 204111, 204122, 204133, 210706, 210717, 210740, 211195, 211650, 212037, 212075, 212467, 210718, 210729, 210762, 210773, 210784, 211139, 211150, 211161, 211173, 211228, 211584, 211595, 211606, 211628, 211639, 212043, 212052, 212074, 212478, 212489, 212500</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -13260,21 +13260,21 @@
         </is>
       </c>
       <c r="J177">
-        <v>1556</v>
+        <v>3891</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665365</t>
+          <t xml:space="preserve">311721371</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-09</t>
+          <t xml:space="preserve">2033-11-10</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slotsvænget 23A</t>
+          <t xml:space="preserve">Eremitageparken 201</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,30 +13326,30 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8864457</t>
+          <t xml:space="preserve">210742, 210743, 210746, 210755, 210757, 210758, 210766, 210768, 210772, 210786, 210744, 210745, 210747, 210748, 210749, 210750, 210787, 210752, 210753, 210754, 210756, 210765, 210767, 210759, 210760, 210761, 210763, 210764, 210769, 210770, 210771, 210774, 210775, 210776, 210777, 210778, 210779, 210780, 210781, 210782, 210783, 210785, 210788, 210789</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J178">
-        <v>1832</v>
+        <v>3112</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665366</t>
+          <t xml:space="preserve">311721371</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-09</t>
+          <t xml:space="preserve">2033-11-10</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorgenfrivej 21</t>
+          <t xml:space="preserve">Eremitageparken 209</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,30 +13401,30 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029965</t>
+          <t xml:space="preserve">210790, 210791, 210792, 211148, 211159, 211170, 211171, 210793, 211138, 211140, 211141, 211142, 211143, 211144, 211147, 211149, 211163, 211166, 211181, 211145, 211146, 211151, 211152, 211153, 211154, 211155, 211156, 211157, 211158, 211160, 211162, 211164, 211165, 211167, 211168, 211169, 211174, 211175, 211176, 211177, 211178, 211179, 211180, 211182</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J179">
-        <v>260</v>
+        <v>3112</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665962</t>
+          <t xml:space="preserve">311721371</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-13</t>
+          <t xml:space="preserve">2033-11-10</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 103</t>
+          <t xml:space="preserve">Eremitageparken 307</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,12 +13476,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">204081, 204082, 204083, 204084, 204085, 204086, 204087, 204088, 204090, 204091, 204092, 204093, 204094, 204095, 204106, 204096, 204097, 204102, 204105, 204109, 204114, 204098, 204101, 204103, 204104, 204107, 204108, 204110, 204112, 204113, 204115, 204116, 204118, 204119, 204117, 204120, 204121, 204123, 204124, 204125, 204126, 204127, 204128</t>
+          <t xml:space="preserve">211578, 211579, 211580, 211592, 211603, 211581, 211591, 211598, 211602, 211609, 211621, 211582, 211583, 211585, 211586, 211587, 211588, 211589, 211590, 211593, 211594, 211596, 211597, 211599, 211600, 211601, 211604, 211605, 211607, 211608, 211610, 211611, 211612, 211613, 211614, 211615, 211616, 211618, 211619, 211620, 211622, 211623, 211625</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J180">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 11</t>
+          <t xml:space="preserve">Eremitageparken 317</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,16 +13551,16 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">204044, 211172, 211184, 211206, 204045, 204056, 210751, 211217, 211617, 211627, 211661, 212015, 212026, 212063, 204067, 204078, 204089, 204100, 204111, 204122, 204133, 210706, 210717, 210740, 211195, 211650, 212037, 212075, 212467, 210718, 210729, 210762, 210773, 210784, 211139, 211150, 211161, 211173, 211228, 211584, 211595, 211606, 211628, 211639, 212043, 212052, 212074, 212478, 212489, 212500</t>
+          <t xml:space="preserve">211626, 211630, 211631, 211634, 211638, 211641, 211649, 211653, 211665, 211669, 211629, 211640, 211662, 211632, 211633, 211635, 211636, 211637, 211642, 211643, 211644, 211645, 211646, 211647, 211648, 211651, 211652, 211654, 211655, 211656, 211657, 211658, 211659, 211660, 211663, 211664, 211666, 211667, 211668, 211670</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J181">
-        <v>3891</v>
+        <v>3112</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -13601,12 +13601,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 201</t>
+          <t xml:space="preserve">Eremitageparken 325</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,16 +13626,16 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">210742, 210743, 210746, 210755, 210757, 210758, 210766, 210768, 210772, 210786, 210744, 210745, 210747, 210748, 210749, 210750, 210787, 210752, 210753, 210754, 210756, 210765, 210767, 210759, 210760, 210761, 210763, 210764, 210769, 210770, 210771, 210774, 210775, 210776, 210777, 210778, 210779, 210780, 210781, 210782, 210783, 210785, 210788, 210789</t>
+          <t xml:space="preserve">211671, 212016, 212017, 212018, 212019, 212020, 212021, 212022, 212023, 212024, 212025, 212027, 212028, 212029, 212030, 212031, 212032, 212033, 212034, 212035, 212036, 212039, 212038, 212040</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J182">
-        <v>3112</v>
+        <v>1476</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
+          <t xml:space="preserve">Person med navne- og adressebeskyttelse</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 209</t>
+          <t xml:space="preserve">Eremitageparken 361</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,16 +13701,16 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">210790, 210791, 210792, 211148, 211159, 211170, 211171, 210793, 211138, 211140, 211141, 211142, 211143, 211144, 211147, 211149, 211163, 211166, 211181, 211145, 211146, 211151, 211152, 211153, 211154, 211155, 211156, 211157, 211158, 211160, 211162, 211164, 211165, 211167, 211168, 211169, 211174, 211175, 211176, 211177, 211178, 211179, 211180, 211182</t>
+          <t xml:space="preserve">212047, 212048, 212051, 212065, 212049, 212050, 212061, 212053, 212054, 212055, 212056, 212062, 212066, 212057, 212058, 212059, 212060, 212064, 212067, 212068, 212069, 212070, 212071, 212072</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
       <c r="J183">
-        <v>3112</v>
+        <v>1476</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 307</t>
+          <t xml:space="preserve">Eremitageparken 367</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13776,16 +13776,16 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">211578, 211579, 211580, 211592, 211603, 211581, 211591, 211598, 211602, 211609, 211621, 211582, 211583, 211585, 211586, 211587, 211588, 211589, 211590, 211593, 211594, 211596, 211597, 211599, 211600, 211601, 211604, 211605, 211607, 211608, 211610, 211611, 211612, 211613, 211614, 211615, 211616, 211618, 211619, 211620, 211622, 211623, 211625</t>
+          <t xml:space="preserve">212073, 212076, 212087, 212091, 212098, 212102, 212109, 212453, 212077, 212078, 212079, 212080, 212081, 212082, 212083, 212084, 212085, 212088, 212089, 212094, 212096, 212101, 212103, 212443, 212451, 212454, 212460, 212090, 212092, 212093, 212095, 212099, 212100, 212104, 212105, 212106, 212107, 212444, 212445, 212446, 212447, 212448, 212449, 212450, 212455, 212456, 212457, 212458, 212459, 212461</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J184">
-        <v>3112</v>
+        <v>3890</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 317</t>
+          <t xml:space="preserve">Eremitageparken 95</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,12 +13851,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">211626, 211630, 211631, 211634, 211638, 211641, 211649, 211653, 211665, 211669, 211629, 211640, 211662, 211632, 211633, 211635, 211636, 211637, 211642, 211643, 211644, 211645, 211646, 211647, 211648, 211651, 211652, 211654, 211655, 211656, 211657, 211658, 211659, 211660, 211663, 211664, 211666, 211667, 211668, 211670</t>
+          <t xml:space="preserve">204046, 204047, 212498, 204048, 204049, 204050, 204065, 212505, 212510, 204051, 204052, 204053, 204054, 204055, 204057, 204058, 204059, 204060, 204061, 204062, 204063, 204064, 204066, 204068, 204069, 204070, 204071, 212509, 204072, 204073, 204074, 204075, 204076, 204077, 204079, 204080, 212499, 212501, 212502, 212503, 212504, 212506, 212507, 212508</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J185">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 325</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,30 +13926,30 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">211671, 212016, 212017, 212018, 212019, 212020, 212021, 212022, 212023, 212024, 212025, 212027, 212028, 212029, 212030, 212031, 212032, 212033, 212034, 212035, 212036, 212039, 212038, 212040</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J186">
-        <v>1476</v>
+        <v>623</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721371</t>
+          <t xml:space="preserve">311725677</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-10</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13976,12 +13976,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Person med navne- og adressebeskyttelse</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 361</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,30 +14001,30 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">212047, 212048, 212051, 212065, 212049, 212050, 212061, 212053, 212054, 212055, 212056, 212062, 212066, 212057, 212058, 212059, 212060, 212064, 212067, 212068, 212069, 212070, 212071, 212072</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J187">
-        <v>1476</v>
+        <v>3933</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721371</t>
+          <t xml:space="preserve">311726115</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-10</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14051,12 +14051,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 367</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,30 +14076,30 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">212073, 212076, 212087, 212091, 212098, 212102, 212109, 212453, 212077, 212078, 212079, 212080, 212081, 212082, 212083, 212084, 212085, 212088, 212089, 212094, 212096, 212101, 212103, 212443, 212451, 212454, 212460, 212090, 212092, 212093, 212095, 212099, 212100, 212104, 212105, 212106, 212107, 212444, 212445, 212446, 212447, 212448, 212449, 212450, 212455, 212456, 212457, 212458, 212459, 212461</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J188">
-        <v>3890</v>
+        <v>1086</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721371</t>
+          <t xml:space="preserve">311726115</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-10</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14126,12 +14126,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velliv Ejendomsinvestering P/S</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eremitageparken 95</t>
+          <t xml:space="preserve">Nøjsomhedsvej 1</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,30 +14151,30 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">204046, 204047, 212498, 204048, 204049, 204050, 204065, 212505, 212510, 204051, 204052, 204053, 204054, 204055, 204057, 204058, 204059, 204060, 204061, 204062, 204063, 204064, 204066, 204068, 204069, 204070, 204071, 212509, 204072, 204073, 204074, 204075, 204076, 204077, 204079, 204080, 212499, 212501, 212502, 212503, 212504, 212506, 212507, 212508</t>
+          <t xml:space="preserve">2061486</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J189">
-        <v>3112</v>
+        <v>935</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311721371</t>
+          <t xml:space="preserve">311726115</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">Dansk Energi Management</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-10</t>
+          <t xml:space="preserve">2033-12-01</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14201,12 +14201,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
+          <t xml:space="preserve">Naturstyrelsen</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -14216,40 +14216,40 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Trepilevej 9</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2930</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">715209, 9166715</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">581</t>
         </is>
       </c>
       <c r="J190">
-        <v>623</v>
+        <v>284</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725677</t>
+          <t xml:space="preserve">311800045</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-11-28</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Toftebæksvej 3A</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">1300781</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,21 +14310,21 @@
         </is>
       </c>
       <c r="J191">
-        <v>3933</v>
+        <v>480</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726115</t>
+          <t xml:space="preserve">311811264</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve">Fried-Energi ApS</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-02-12</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Klintevej 14</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,30 +14376,30 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2065128</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J192">
-        <v>1086</v>
+        <v>372</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726115</t>
+          <t xml:space="preserve">311824399</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-04-10</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøjsomhedsvej 1</t>
+          <t xml:space="preserve">Christian X's Alle 117</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,30 +14451,30 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2061486</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J193">
-        <v>935</v>
+        <v>560</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311726115</t>
+          <t xml:space="preserve">311862495</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energi Management</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-01</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14501,12 +14501,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturstyrelsen</t>
+          <t xml:space="preserve">Lyngby-Taarbæk Kommune</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -14516,40 +14516,40 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trepilevej 9</t>
+          <t xml:space="preserve">Christian X's Alle 117</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930</t>
+          <t xml:space="preserve">2800</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">715209, 9166715</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">581</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J194">
-        <v>284</v>
+        <v>705</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800045</t>
+          <t xml:space="preserve">311862485</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-28</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftebæksvej 3A</t>
+          <t xml:space="preserve">Engelsborgvej 66</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,30 +14601,30 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300781</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J195">
-        <v>480</v>
+        <v>1047</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311811264</t>
+          <t xml:space="preserve">311862497</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fried-Energi ApS</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-12</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klintevej 14</t>
+          <t xml:space="preserve">Engelsborgvej 66</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,30 +14676,30 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065128</t>
+          <t xml:space="preserve">2064948</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J196">
-        <v>372</v>
+        <v>1054</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311824399</t>
+          <t xml:space="preserve">311862490</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-10</t>
+          <t xml:space="preserve">2035-10-16</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 117</t>
+          <t xml:space="preserve">Gammel Bagsværdvej 41</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14756,15 +14756,15 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J197">
-        <v>560</v>
+        <v>257</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862495</t>
+          <t xml:space="preserve">311862494</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Christian X's Alle 117</t>
+          <t xml:space="preserve">Kongevejen 51</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,30 +14826,30 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2027998</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J198">
-        <v>705</v>
+        <v>366</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862485</t>
+          <t xml:space="preserve">311907609</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">B.F. Byggeservice ApS</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-06-11</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,40 +14891,40 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelsborgvej 66</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J199">
-        <v>1047</v>
+        <v>3540</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862497</t>
+          <t xml:space="preserve">311926685</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,40 +14966,40 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engelsborgvej 66</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J200">
-        <v>1054</v>
+        <v>428</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862490</t>
+          <t xml:space="preserve">311926685</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,40 +15041,40 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Bagsværdvej 41</t>
+          <t xml:space="preserve">Kongsvænget 10</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800</t>
+          <t xml:space="preserve">2830</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064948</t>
+          <t xml:space="preserve">2030815</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J201">
-        <v>257</v>
+        <v>431</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311862494</t>
+          <t xml:space="preserve">311926685</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-10-16</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 51</t>
+          <t xml:space="preserve">Nøjsomhedsvej 30</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027998</t>
+          <t xml:space="preserve">2060987</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,21 +15135,21 @@
         </is>
       </c>
       <c r="J202">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311907609</t>
+          <t xml:space="preserve">311926684</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">B.F. Byggeservice ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-11</t>
+          <t xml:space="preserve">2036-09-18</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">

--- a/public/exports-with-coowners/11715311.xlsx
+++ b/public/exports-with-coowners/11715311.xlsx
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311017836</t>
+          <t xml:space="preserve">311017829</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
